--- a/artfynd/A 25888-2026 artfynd.xlsx
+++ b/artfynd/A 25888-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103915600</v>
+        <v>130241481</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N , Upl</t>
+          <t>Väst om myren, Väst om myren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692766.6382161319</v>
+        <v>692673</v>
       </c>
       <c r="R2" t="n">
-        <v>6604248.580600896</v>
+        <v>6604208</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,76 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Tomas Fridström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Tomas Fridström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121802057</v>
+        <v>130253847</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m nordväst om Dalsättra, Storskogen, Upl</t>
+          <t>O. Skeppsbol, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692644</v>
+        <v>692674</v>
       </c>
       <c r="R3" t="n">
-        <v>6604154</v>
+        <v>6604228</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,85 +868,70 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121802077</v>
+        <v>103915065</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m nordväst om Dalsättra, Storskogen, Upl</t>
+          <t>N Dalsättra, Tärnanområdet , Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692644</v>
+        <v>692856</v>
       </c>
       <c r="R4" t="n">
-        <v>6604146</v>
+        <v>6604153</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,17 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 grupper. Alla tre bestånd invid gamla tallar i sluttning nedanför hällmark. Nyckelbiotop.</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,29 +969,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130240895</v>
+        <v>103915149</v>
       </c>
       <c r="B5" t="n">
-        <v>97828</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,37 +998,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väst om myren, Väst om myren, Upl</t>
+          <t>N Dalsättra, Tärnanområdet , Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692726</v>
+        <v>692868</v>
       </c>
       <c r="R5" t="n">
-        <v>6604221</v>
+        <v>6604161</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1073,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130242336</v>
+        <v>103915600</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,37 +1096,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalsättra, Dalsättra, Upl</t>
+          <t>N , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692734</v>
+        <v>692767</v>
       </c>
       <c r="R6" t="n">
-        <v>6604255</v>
+        <v>6604248</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,15 +1171,1770 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114948001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SO Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>692625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6604172</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130241428</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väst om myren, Väst om myren, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>692648</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6604194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121803274</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m nordväst om Dalsättra , Storskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>692664</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6604167</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103915226</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Dalsättra, Tärnanområdet , Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>692849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6604168</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130253848</v>
+      </c>
+      <c r="B11" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>O. Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>692698</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6604248</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre kläckhål i fnösketicka</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103915262</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Dalsättra, Tärnanområdet , Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>692849</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6604166</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124127413</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sumpskogen vid vändplanen, Sumpskogen vid vändplanen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>692939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6604187</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130242336</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dalsättra, Dalsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>692734</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6604255</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121801973</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vitmossetorpet, Vitmossetorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>692664</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6604210</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121802056</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vitmossetorpet, Vitmossetorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>692649</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6604203</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121802057</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m nordväst om Dalsättra, Storskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>692644</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6604154</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121802077</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m nordväst om Dalsättra, Storskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>692644</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6604146</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 grupper. Alla tre bestånd invid gamla tallar i sluttning nedanför hällmark. Nyckelbiotop.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121802231</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vitmossetorpet, Vitmossetorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>692640</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6604156</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121802242</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m nordväst om Dalsättra , Storskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>692654</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6604121</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103915027</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N Dalsättra, Tärnanområdet , Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>692856</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6604153</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130240895</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Väst om myren, Väst om myren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>692726</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6604221</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25888-2026 artfynd.xlsx
+++ b/artfynd/A 25888-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130253847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915065</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915149</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114948001</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121803274</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130253848</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915262</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124127413</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242336</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121801973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2265,6 +2340,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121802056</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2376,6 +2456,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121802057</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121802077</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2619,6 +2709,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121802231</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121802242</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103915027</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2935,8 +3040,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130240895</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>